--- a/inst/testdata/registryid/frs_testpoints_100.xlsx
+++ b/inst/testdata/registryid/frs_testpoints_100.xlsx
@@ -11,6 +11,17 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>num</t>
+  </si>
+  <si>
+    <t>REGISTRY_ID</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,816 +365,812 @@
   <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>REGISTRY_ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>110044478142</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>110070322615</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>110024367308</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>110044415282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>110001690590</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>110024314240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>110071073502</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>110001779923</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>110005193566</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>110070754842</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>110068891783</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>110005261661</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>110004104460</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>110068888500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>110045849436</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>110004325089</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>110007834656</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>110045802244</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>110070410523</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>110007705705</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>110002828370</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>110070413341</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>110070550172</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>110002857329</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>110064894422</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>110070531028</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>110065467382</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>110064930712</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>110060252186</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>110065477077</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>110072127939</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>110059981355</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>110071669418</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>110071494182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>110029462766</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>110071148779</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>110071961965</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>110029355374</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>110070224623</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>110071382724</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>110055821847</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>110070243123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>110070040769</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>110055760270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>110072083417</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>110071951840</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>110022571689</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>110070053582</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>110072113628</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>110071463275</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>110071346716</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>110022433623</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>110019389696</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>110071488613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
-        <v>110011649797</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>110070935042</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
-        <v>110069997907</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>110019351397</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
-        <v>110068209799</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>110071945181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32">
-        <v>110015562443</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>110011594408</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
-        <v>110070637122</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>110070016211</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
-        <v>110032076303</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>110068204473</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>110041384604</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>110015521602</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
-        <v>110069645566</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>110070590552</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
-        <v>110009656292</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>110032039586</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
-        <v>110033806665</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>110041321469</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
-        <v>110018264402</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>110069718906</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
-        <v>110066476450</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>110009611722</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
-        <v>110018586779</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>110072219235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
-        <v>110070669298</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>110072028887</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
-        <v>110010969498</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>110071924626</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
-        <v>110040125922</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>110033727377</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
-        <v>110032967136</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>110018213672</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
-        <v>110068558821</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>110071962337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
-        <v>110066115135</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>110066450101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
-        <v>110010924250</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>110018527986</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
-        <v>110020685329</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>110070600341</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50">
-        <v>110071916833</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>110010887754</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51">
-        <v>110070877530</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>110040050084</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52">
-        <v>110071427692</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>110071991797</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
-        <v>110033110924</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>110032830541</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54">
-        <v>110019247885</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>110068553425</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55">
-        <v>110068904626</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>110066102167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
-        <v>110070514300</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>110010799564</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
-        <v>110071347440</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>110020495212</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58">
-        <v>110066641432</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>110071319958</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
-        <v>110070454583</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>110070683822</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60">
-        <v>110071478903</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>110071843236</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61">
-        <v>110070913302</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>110071061482</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62">
-        <v>110071470907</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>110032940557</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63">
-        <v>110017453325</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>110019208800</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64">
-        <v>110036161248</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>110068900577</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65">
-        <v>110003652182</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>110071946697</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66">
-        <v>110065846954</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>110070492772</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67">
-        <v>110066564541</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>110070936436</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68">
-        <v>110071924258</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>110066609021</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69">
-        <v>110070087734</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>110070452426</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70">
-        <v>110066470811</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>110071102141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71">
-        <v>110044346213</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>110072221659</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72">
-        <v>110033179922</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>110070696353</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73">
-        <v>110055506126</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>110071094126</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74">
-        <v>110025100744</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>110017326160</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75">
-        <v>110014005469</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>110036042010</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76">
-        <v>110010666234</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>110071739015</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77">
-        <v>110039302359</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>110003700781</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78">
-        <v>110019158285</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>110065844625</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79">
-        <v>110071931468</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>110071970497</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80">
-        <v>110071065603</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>110066533246</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81">
-        <v>110027961329</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>110071332093</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82">
-        <v>110001763930</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>110070104347</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83">
-        <v>110071669740</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>110066444413</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84">
-        <v>110011002887</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>110044245457</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85">
-        <v>110012013579</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>110033001230</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86">
-        <v>110041445889</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>110055399162</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87">
-        <v>110067814388</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>110025045172</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88">
-        <v>110046481669</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>110013928483</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89">
-        <v>110070274632</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>110010621808</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90">
-        <v>110033824486</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>110039263640</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91">
-        <v>110014079219</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>110019119354</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92">
-        <v>110071295868</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>110071344392</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93">
-        <v>110070522535</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>110070732541</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94">
-        <v>110018578323</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>110027307171</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95">
-        <v>110068788985</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>110001829004</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96">
-        <v>110014420885</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>110071945428</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97">
-        <v>110066477529</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>110071149092</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98">
-        <v>110064432886</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>110010924250</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99">
-        <v>110065969465</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>110011975648</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100">
-        <v>110058479766</v>
-      </c>
-    </row>
-    <row r="101">
+        <v>110041398127</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101">
-        <v>110064640508</v>
+        <v>110067809697</v>
       </c>
     </row>
   </sheetData>
